--- a/project/DemoGuru99.com/Demoguru 99.xlsx
+++ b/project/DemoGuru99.com/Demoguru 99.xlsx
@@ -4,11 +4,11 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="120" windowWidth="20115" windowHeight="7755"/>
+    <workbookView xWindow="240" yWindow="120" windowWidth="20115" windowHeight="7755" activeTab="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
+    <sheet name="Test Case" sheetId="1" r:id="rId1"/>
+    <sheet name="HLR" sheetId="2" r:id="rId2"/>
     <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="145621"/>
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="253" uniqueCount="128">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="267" uniqueCount="142">
   <si>
     <t>Test Case ID</t>
   </si>
@@ -405,13 +405,55 @@
   <si>
     <t>enter password
 click login</t>
+  </si>
+  <si>
+    <t>Functionality ID</t>
+  </si>
+  <si>
+    <t>Functionality Name</t>
+  </si>
+  <si>
+    <t>Description</t>
+  </si>
+  <si>
+    <t>4.14.4</t>
+  </si>
+  <si>
+    <t>check open icon</t>
+  </si>
+  <si>
+    <t>click on open icon</t>
+  </si>
+  <si>
+    <t>Open website</t>
+  </si>
+  <si>
+    <t>The system shall allow to oen website</t>
+  </si>
+  <si>
+    <t>Check menues</t>
+  </si>
+  <si>
+    <t>Check submenues</t>
+  </si>
+  <si>
+    <t>Menu should open properly</t>
+  </si>
+  <si>
+    <t>submenues should be open properly</t>
+  </si>
+  <si>
+    <t>login account</t>
+  </si>
+  <si>
+    <t>login should be prooperly</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -436,6 +478,14 @@
       <u/>
       <sz val="11"/>
       <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -483,7 +533,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
@@ -517,6 +567,12 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1793,12 +1849,18 @@
       <c r="A34" s="4">
         <v>4</v>
       </c>
-      <c r="B34" s="4"/>
-      <c r="C34" s="4"/>
+      <c r="B34" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="C34" s="4" t="s">
+        <v>132</v>
+      </c>
       <c r="D34" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="E34" s="9"/>
+      <c r="E34" s="9" t="s">
+        <v>133</v>
+      </c>
       <c r="F34" s="9"/>
       <c r="G34" s="5"/>
       <c r="H34" s="5"/>
@@ -1895,9 +1957,207 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1"/>
+  <dimension ref="A1:C30"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="1" width="15.85546875" customWidth="1"/>
+    <col min="2" max="2" width="28.42578125" customWidth="1"/>
+    <col min="3" max="3" width="28.85546875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" s="16" t="s">
+        <v>128</v>
+      </c>
+      <c r="B1" s="16" t="s">
+        <v>129</v>
+      </c>
+      <c r="C1" s="16" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A2" s="17">
+        <v>1</v>
+      </c>
+      <c r="B2" s="17" t="s">
+        <v>134</v>
+      </c>
+      <c r="C2" s="17" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" s="17">
+        <v>2</v>
+      </c>
+      <c r="B3" s="17" t="s">
+        <v>136</v>
+      </c>
+      <c r="C3" s="17" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A4" s="17">
+        <v>3</v>
+      </c>
+      <c r="B4" s="17" t="s">
+        <v>137</v>
+      </c>
+      <c r="C4" s="17" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" s="17">
+        <v>4</v>
+      </c>
+      <c r="B5" s="17" t="s">
+        <v>140</v>
+      </c>
+      <c r="C5" s="17" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" s="17">
+        <v>5</v>
+      </c>
+      <c r="B6" s="17"/>
+      <c r="C6" s="17"/>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" s="17">
+        <v>6</v>
+      </c>
+      <c r="B7" s="17"/>
+      <c r="C7" s="17"/>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" s="17">
+        <v>7</v>
+      </c>
+      <c r="B8" s="17"/>
+      <c r="C8" s="17"/>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" s="17">
+        <v>8</v>
+      </c>
+      <c r="B9" s="17"/>
+      <c r="C9" s="17"/>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" s="17">
+        <v>9</v>
+      </c>
+      <c r="B10" s="17"/>
+      <c r="C10" s="17"/>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" s="17">
+        <v>10</v>
+      </c>
+      <c r="B11" s="17"/>
+      <c r="C11" s="17"/>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12" s="17">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13" s="17">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A14" s="17">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A15" s="17">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A16" s="17">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A17" s="17">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A18" s="17">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A19" s="17">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A20" s="17">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A21" s="17">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A22" s="17">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A23" s="17">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A24" s="17">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A25" s="17">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A26" s="17">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A27" s="17">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A28" s="17">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A29" s="17">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A30" s="17">
+        <v>29</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
